--- a/docs/governanca-agentes-fluxos.xlsx
+++ b/docs/governanca-agentes-fluxos.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Camadas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Agentes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Prompts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Skills" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rules" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Onde_esta" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Solto_ou_fraco" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Receitas" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agentes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Onde_esta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solto_ou_fraco" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Receitas" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,13 +436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Lint e testes</t>
+          <t>Lint, audit-dnd35-js, E2E Playwright</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -699,27 +699,52 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ADRs</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>docs/adr/</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Decisões irreversíveis (monólito, Tormenta, dnd5e, apps adiado)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Manual / @ no chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Tracking manual</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>MELHORIAS.md, HISTORICO_EVOLUCAO.md</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Débito e histórico</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Solto — não ligado a agentes</t>
         </is>
@@ -1683,7 +1708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1847,66 +1872,151 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Dados Neon?</t>
+          <t>Auth refresh/OAuth?</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>.cursor/skills/arena-producao-dados-neon-render/</t>
+          <t>docs/auth-sessao-oauth.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Guarda terminal?</t>
+          <t>Livros → dados/RF?</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>.github/hooks/</t>
+          <t>docs/livros-para-dados.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Guia markdown?</t>
+          <t>Matriz RF × código?</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Este doc</t>
+          <t>Doc</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>docs/governanca-agentes-fluxos.md</t>
+          <t>docs/requisitos-cobertura-matrix.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Auditoria JS dnd35?</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Doc + script</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>docs/dnd35-js-auditoria-2026-06.md, scripts/audit-dnd35-js.sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>E2E Playwright?</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Doc</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>docs/e2e-playwright-arena.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Dados Neon?</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>.cursor/skills/arena-producao-dados-neon-render/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Guarda terminal?</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Hook</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>.github/hooks/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Guia markdown?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Este doc</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>docs/governanca-agentes-fluxos.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Planilha?</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Excel</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>docs/governanca-agentes-fluxos.xlsx</t>
         </is>
@@ -2078,7 +2188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2360,60 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Auditoria JS dnd35</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>docs/dnd35-js-auditoria-2026-06.md</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>scripts/audit-dnd35-js.sh</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fase 1 quick wins</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>E2E + ESLint</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Auth/OAuth produção</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>docs/auth-sessao-oauth.md</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Render env GOOGLE_OAUTH_*</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>PRE_DEPLOY_CHECKLIST</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
